--- a/baseline_models/pernio_runs.xlsx
+++ b/baseline_models/pernio_runs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-315" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" state="visible" r:id="rId1"/>
@@ -45447,17 +45447,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-30 11:26:12</t>
+          <t>2026-10-14 12:14:16</t>
         </is>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.953059007127104</v>
+        <v>0.8758538524202817</v>
       </c>
       <c r="F2" t="n">
-        <v>1.009386886196531</v>
+        <v>0.9417457314648419</v>
       </c>
     </row>
     <row r="3">
@@ -45473,17 +45473,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-30 11:26:24</t>
+          <t>2026-10-14 12:14:30</t>
         </is>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.953059007127104</v>
+        <v>0.8758538524202817</v>
       </c>
       <c r="F3" t="n">
-        <v>1.009386886196531</v>
+        <v>0.9417457314648419</v>
       </c>
     </row>
     <row r="4">
@@ -45499,17 +45499,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-30 11:26:37</t>
+          <t>2026-10-14 12:14:47</t>
         </is>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.953059007127104</v>
+        <v>0.8758538524202817</v>
       </c>
       <c r="F4" t="n">
-        <v>1.009386886196531</v>
+        <v>0.9417457314648419</v>
       </c>
     </row>
     <row r="5">
@@ -45525,17 +45525,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-30 11:26:56</t>
+          <t>2026-10-14 12:15:01</t>
         </is>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.953059007127104</v>
+        <v>0.8758538524202817</v>
       </c>
       <c r="F5" t="n">
-        <v>1.009386886196531</v>
+        <v>0.9417457314648419</v>
       </c>
     </row>
     <row r="6">
@@ -45551,17 +45551,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-30 11:27:14</t>
+          <t>2026-10-14 12:15:14</t>
         </is>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9430364622171142</v>
+        <v>0.8667516092199194</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9940210210729403</v>
+        <v>0.9284251947332995</v>
       </c>
     </row>
     <row r="7">
@@ -45577,17 +45577,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-30 11:27:28</t>
+          <t>2026-10-14 12:15:27</t>
         </is>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9430364622171142</v>
+        <v>0.8667516092199194</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9940210210729403</v>
+        <v>0.9284251947332995</v>
       </c>
     </row>
     <row r="8">
@@ -45603,17 +45603,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-30 11:27:42</t>
+          <t>2026-10-14 12:15:41</t>
         </is>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.165136408724684</v>
+        <v>1.119345198789853</v>
       </c>
       <c r="F8" t="n">
-        <v>1.251783831799019</v>
+        <v>1.205538810288076</v>
       </c>
     </row>
     <row r="9">
@@ -45629,17 +45629,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-30 11:27:56</t>
+          <t>2026-10-14 12:15:54</t>
         </is>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.165136408724684</v>
+        <v>1.119345198789853</v>
       </c>
       <c r="F9" t="n">
-        <v>1.251783831799019</v>
+        <v>1.205538810288076</v>
       </c>
     </row>
     <row r="10">
@@ -45655,17 +45655,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-30 11:28:09</t>
+          <t>2026-10-14 12:16:08</t>
         </is>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1.008792721565236</v>
+        <v>0.9446460354922549</v>
       </c>
       <c r="F10" t="n">
-        <v>1.293787578164951</v>
+        <v>1.244548790608557</v>
       </c>
     </row>
     <row r="11">
@@ -45681,17 +45681,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-30 11:28:22</t>
+          <t>2026-10-14 12:16:21</t>
         </is>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.008792721565236</v>
+        <v>0.9446460354922549</v>
       </c>
       <c r="F11" t="n">
-        <v>1.293787578164951</v>
+        <v>1.244548790608557</v>
       </c>
     </row>
     <row r="12">
@@ -45707,17 +45707,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-30 11:28:34</t>
+          <t>2026-10-14 12:16:34</t>
         </is>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.165136408724684</v>
+        <v>1.119345198789853</v>
       </c>
       <c r="F12" t="n">
-        <v>1.251783831799019</v>
+        <v>1.205538810288076</v>
       </c>
     </row>
     <row r="13">
@@ -45733,17 +45733,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-30 11:28:46</t>
+          <t>2026-10-14 12:16:48</t>
         </is>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.165136408724684</v>
+        <v>1.119345198789853</v>
       </c>
       <c r="F13" t="n">
-        <v>1.251783831799019</v>
+        <v>1.205538810288076</v>
       </c>
     </row>
     <row r="14">
@@ -45759,17 +45759,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-30 11:29:02</t>
+          <t>2026-10-14 12:17:00</t>
         </is>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.008792721565236</v>
+        <v>0.9446460354922549</v>
       </c>
       <c r="F14" t="n">
-        <v>1.293787578164951</v>
+        <v>1.244548790608557</v>
       </c>
     </row>
     <row r="15">
@@ -45785,17 +45785,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-30 11:29:15</t>
+          <t>2026-10-14 12:17:14</t>
         </is>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.008792721565236</v>
+        <v>0.9446460354922549</v>
       </c>
       <c r="F15" t="n">
-        <v>1.293787578164951</v>
+        <v>1.244548790608557</v>
       </c>
     </row>
     <row r="16">
@@ -45811,17 +45811,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-30 11:29:29</t>
+          <t>2026-10-14 12:17:26</t>
         </is>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1.14783819608205</v>
+        <v>1.007184557266728</v>
       </c>
       <c r="F16" t="n">
-        <v>1.237263137469301</v>
+        <v>1.193797880436772</v>
       </c>
     </row>
     <row r="17">
@@ -45837,17 +45837,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-30 11:29:43</t>
+          <t>2026-10-14 12:17:39</t>
         </is>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.14783819608205</v>
+        <v>1.007184557266728</v>
       </c>
       <c r="F17" t="n">
-        <v>1.237263137469301</v>
+        <v>1.193797880436772</v>
       </c>
     </row>
     <row r="18">
@@ -45863,17 +45863,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-30 11:29:57</t>
+          <t>2026-10-14 12:17:53</t>
         </is>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9861626061805566</v>
+        <v>0.9227740012244507</v>
       </c>
       <c r="F18" t="n">
-        <v>1.266526085018842</v>
+        <v>1.227311461910088</v>
       </c>
     </row>
     <row r="19">
@@ -45889,17 +45889,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-30 11:30:11</t>
+          <t>2026-10-14 12:18:05</t>
         </is>
       </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9861626061805566</v>
+        <v>0.9227740012244507</v>
       </c>
       <c r="F19" t="n">
-        <v>1.266526085018842</v>
+        <v>1.227311461910088</v>
       </c>
     </row>
     <row r="20">
@@ -45915,17 +45915,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-30 11:30:28</t>
+          <t>2026-10-14 12:18:19</t>
         </is>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7031605094647498</v>
+        <v>0.6856870415335626</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6986904653734356</v>
+        <v>0.680068759671007</v>
       </c>
     </row>
     <row r="21">
@@ -45941,17 +45941,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-30 11:30:43</t>
+          <t>2026-10-14 12:18:33</t>
         </is>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7031605094647498</v>
+        <v>0.6856870415335626</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6986904653734356</v>
+        <v>0.680068759671007</v>
       </c>
     </row>
     <row r="22">
@@ -45967,17 +45967,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-30 11:30:58</t>
+          <t>2026-10-14 12:18:45</t>
         </is>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7191755725330925</v>
+        <v>0.7010988531395375</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7247734211780705</v>
+        <v>0.7054183959193792</v>
       </c>
     </row>
     <row r="23">
@@ -45993,17 +45993,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-30 11:31:12</t>
+          <t>2026-10-14 12:18:57</t>
         </is>
       </c>
       <c r="D23" t="b">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7191755725330925</v>
+        <v>0.7010988531395375</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7247734211780705</v>
+        <v>0.7054183959193792</v>
       </c>
     </row>
     <row r="24">
@@ -46019,17 +46019,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-30 11:31:27</t>
+          <t>2026-10-14 12:19:11</t>
         </is>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7031605094647498</v>
+        <v>0.6856870415335626</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6986904653734356</v>
+        <v>0.680068759671007</v>
       </c>
     </row>
     <row r="25">
@@ -46045,17 +46045,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-30 11:31:42</t>
+          <t>2026-10-14 12:19:26</t>
         </is>
       </c>
       <c r="D25" t="b">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7031605094647498</v>
+        <v>0.6856870415335626</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6986904653734356</v>
+        <v>0.680068759671007</v>
       </c>
     </row>
     <row r="26">
@@ -46071,17 +46071,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-30 11:31:58</t>
+          <t>2026-10-14 12:19:41</t>
         </is>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7191755725330925</v>
+        <v>0.7010988531395375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7247734211780705</v>
+        <v>0.7054183959193792</v>
       </c>
     </row>
     <row r="27">
@@ -46097,17 +46097,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-30 11:32:14</t>
+          <t>2026-10-14 12:19:54</t>
         </is>
       </c>
       <c r="D27" t="b">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7191755725330925</v>
+        <v>0.7010988531395375</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7247734211780705</v>
+        <v>0.7054183959193792</v>
       </c>
     </row>
     <row r="28">
@@ -46123,17 +46123,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-30 11:32:28</t>
+          <t>2026-10-14 12:20:07</t>
         </is>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6961602168801996</v>
+        <v>0.6789022736365447</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6978939535876277</v>
+        <v>0.6818860115962418</v>
       </c>
     </row>
     <row r="29">
@@ -46149,17 +46149,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-30 11:32:43</t>
+          <t>2026-10-14 12:20:20</t>
         </is>
       </c>
       <c r="D29" t="b">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6961602168801996</v>
+        <v>0.6789022736365447</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6978939535876277</v>
+        <v>0.6818860115962418</v>
       </c>
     </row>
     <row r="30">
@@ -46175,17 +46175,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-30 11:33:09</t>
+          <t>2026-10-14 12:20:38</t>
         </is>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.711978038039861</v>
+        <v>0.6941239737650787</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7125446810694043</v>
+        <v>0.6934868745367244</v>
       </c>
     </row>
     <row r="31">
@@ -46201,17 +46201,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-30 11:33:34</t>
+          <t>2026-10-14 12:20:56</t>
         </is>
       </c>
       <c r="D31" t="b">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.711978038039861</v>
+        <v>0.6941239737650787</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7125446810694043</v>
+        <v>0.6934868745367244</v>
       </c>
     </row>
     <row r="32">
@@ -46227,17 +46227,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-30 11:33:50</t>
+          <t>2026-10-14 12:21:09</t>
         </is>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.05146653982795</v>
+        <v>0.9736241438380847</v>
       </c>
       <c r="F32" t="n">
-        <v>1.054997238374501</v>
+        <v>0.9819157487739296</v>
       </c>
     </row>
     <row r="33">
@@ -46253,17 +46253,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-30 11:34:07</t>
+          <t>2026-10-14 12:21:22</t>
         </is>
       </c>
       <c r="D33" t="b">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.05146653982795</v>
+        <v>0.9736241438380847</v>
       </c>
       <c r="F33" t="n">
-        <v>1.054997238374501</v>
+        <v>0.9819157487739296</v>
       </c>
     </row>
     <row r="34">
@@ -46279,17 +46279,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-30 11:34:24</t>
+          <t>2026-10-14 12:21:36</t>
         </is>
       </c>
       <c r="D34" t="b">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1.063121584616106</v>
+        <v>0.9634813239462012</v>
       </c>
       <c r="F34" t="n">
-        <v>1.070057046454142</v>
+        <v>0.9891337921887127</v>
       </c>
     </row>
     <row r="35">
@@ -46305,17 +46305,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-30 11:34:40</t>
+          <t>2026-10-14 12:21:48</t>
         </is>
       </c>
       <c r="D35" t="b">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.063121584616106</v>
+        <v>0.9634813239462012</v>
       </c>
       <c r="F35" t="n">
-        <v>1.070057046454142</v>
+        <v>0.9891337921887127</v>
       </c>
     </row>
     <row r="36">
@@ -46331,17 +46331,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-30 11:34:56</t>
+          <t>2026-10-14 12:22:03</t>
         </is>
       </c>
       <c r="D36" t="b">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1.05146653982795</v>
+        <v>0.9736241438380847</v>
       </c>
       <c r="F36" t="n">
-        <v>1.054997238374501</v>
+        <v>0.9819157487739296</v>
       </c>
     </row>
     <row r="37">
@@ -46357,17 +46357,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-06-30 11:35:11</t>
+          <t>2026-10-14 12:22:16</t>
         </is>
       </c>
       <c r="D37" t="b">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.05146653982795</v>
+        <v>0.9736241438380847</v>
       </c>
       <c r="F37" t="n">
-        <v>1.054997238374501</v>
+        <v>0.9819157487739296</v>
       </c>
     </row>
     <row r="38">
@@ -46383,17 +46383,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-06-30 11:35:28</t>
+          <t>2026-10-14 12:22:30</t>
         </is>
       </c>
       <c r="D38" t="b">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.063121584616106</v>
+        <v>0.9634813239462012</v>
       </c>
       <c r="F38" t="n">
-        <v>1.070057046454142</v>
+        <v>0.9891337921887127</v>
       </c>
     </row>
     <row r="39">
@@ -46409,17 +46409,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-06-30 11:35:44</t>
+          <t>2026-10-14 12:22:43</t>
         </is>
       </c>
       <c r="D39" t="b">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.063121584616106</v>
+        <v>0.9634813239462012</v>
       </c>
       <c r="F39" t="n">
-        <v>1.070057046454142</v>
+        <v>0.9891337921887127</v>
       </c>
     </row>
     <row r="40">
@@ -46435,17 +46435,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-06-30 11:36:00</t>
+          <t>2026-10-14 12:22:54</t>
         </is>
       </c>
       <c r="D40" t="b">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1.040327080791412</v>
+        <v>0.9633660033523102</v>
       </c>
       <c r="F40" t="n">
-        <v>1.044352149816356</v>
+        <v>0.976182031032175</v>
       </c>
     </row>
     <row r="41">
@@ -46461,17 +46461,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-06-30 11:36:17</t>
+          <t>2026-10-14 12:23:06</t>
         </is>
       </c>
       <c r="D41" t="b">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.040327080791412</v>
+        <v>0.9633660033523102</v>
       </c>
       <c r="F41" t="n">
-        <v>1.044352149816356</v>
+        <v>0.976182031032175</v>
       </c>
     </row>
     <row r="42">
@@ -46487,17 +46487,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-30 11:36:33</t>
+          <t>2026-10-14 12:23:20</t>
         </is>
       </c>
       <c r="D42" t="b">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1.051359881286321</v>
+        <v>0.9510731595923477</v>
       </c>
       <c r="F42" t="n">
-        <v>1.058817011065897</v>
+        <v>0.9683147498657767</v>
       </c>
     </row>
     <row r="43">
@@ -46513,17 +46513,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-06-30 11:36:48</t>
+          <t>2026-10-14 12:23:35</t>
         </is>
       </c>
       <c r="D43" t="b">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.051359881286321</v>
+        <v>0.9510731595923477</v>
       </c>
       <c r="F43" t="n">
-        <v>1.058817011065897</v>
+        <v>0.9683147498657767</v>
       </c>
     </row>
     <row r="44">
@@ -46539,17 +46539,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-07-02 11:44:56</t>
+          <t>2026-10-14 12:23:53</t>
         </is>
       </c>
       <c r="D44" t="b">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.019905965496732</v>
+        <v>0.9435683342339583</v>
       </c>
       <c r="F44" t="n">
-        <v>1.056195607511379</v>
+        <v>0.9692273107753244</v>
       </c>
     </row>
     <row r="45">
@@ -46565,17 +46565,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-07-02 11:45:07</t>
+          <t>2026-10-14 12:24:12</t>
         </is>
       </c>
       <c r="D45" t="b">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.019905965496732</v>
+        <v>0.9435683342339583</v>
       </c>
       <c r="F45" t="n">
-        <v>1.056195607511379</v>
+        <v>0.9692273107753244</v>
       </c>
     </row>
     <row r="46">
@@ -46591,17 +46591,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-02 11:45:19</t>
+          <t>2026-10-14 12:24:24</t>
         </is>
       </c>
       <c r="D46" t="b">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1.030219347311063</v>
+        <v>0.9320835853104928</v>
       </c>
       <c r="F46" t="n">
-        <v>1.071591606319162</v>
+        <v>0.9808114786841542</v>
       </c>
     </row>
     <row r="47">
@@ -46617,17 +46617,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-02 11:45:32</t>
+          <t>2026-10-14 12:24:36</t>
         </is>
       </c>
       <c r="D47" t="b">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.030219347311063</v>
+        <v>0.9320835853104928</v>
       </c>
       <c r="F47" t="n">
-        <v>1.071591606319162</v>
+        <v>0.9808114786841542</v>
       </c>
     </row>
     <row r="48">
@@ -46643,17 +46643,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-02 11:45:46</t>
+          <t>2026-10-14 12:24:54</t>
         </is>
       </c>
       <c r="D48" t="b">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1.019905965496732</v>
+        <v>0.9435683342339583</v>
       </c>
       <c r="F48" t="n">
-        <v>1.056195607511379</v>
+        <v>0.9692273107753244</v>
       </c>
     </row>
     <row r="49">
@@ -46669,17 +46669,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-07-02 11:45:59</t>
+          <t>2026-10-14 12:25:12</t>
         </is>
       </c>
       <c r="D49" t="b">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.019905965496732</v>
+        <v>0.9435683342339583</v>
       </c>
       <c r="F49" t="n">
-        <v>1.056195607511379</v>
+        <v>0.9692273107753244</v>
       </c>
     </row>
     <row r="50">
@@ -46695,17 +46695,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-07-02 11:46:11</t>
+          <t>2026-10-14 12:25:23</t>
         </is>
       </c>
       <c r="D50" t="b">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.030219347311063</v>
+        <v>0.9320835853104928</v>
       </c>
       <c r="F50" t="n">
-        <v>1.071591606319162</v>
+        <v>0.9808114786841542</v>
       </c>
     </row>
     <row r="51">
@@ -46721,17 +46721,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-07-02 11:46:23</t>
+          <t>2026-10-14 12:25:38</t>
         </is>
       </c>
       <c r="D51" t="b">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.030219347311063</v>
+        <v>0.9320835853104928</v>
       </c>
       <c r="F51" t="n">
-        <v>1.071591606319162</v>
+        <v>0.9808114786841542</v>
       </c>
     </row>
     <row r="52">
@@ -46747,17 +46747,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-07-02 11:46:36</t>
+          <t>2026-10-14 12:25:50</t>
         </is>
       </c>
       <c r="D52" t="b">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1.009061033854995</v>
+        <v>0.9336548783897995</v>
       </c>
       <c r="F52" t="n">
-        <v>1.047906022318845</v>
+        <v>0.9750126511274657</v>
       </c>
     </row>
     <row r="53">
@@ -46773,17 +46773,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-07-02 11:46:48</t>
+          <t>2026-10-14 12:26:01</t>
         </is>
       </c>
       <c r="D53" t="b">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.009061033854995</v>
+        <v>0.9336548783897995</v>
       </c>
       <c r="F53" t="n">
-        <v>1.047906022318845</v>
+        <v>0.9750126511274657</v>
       </c>
     </row>
     <row r="54">
@@ -46799,17 +46799,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-07-02 11:47:00</t>
+          <t>2026-10-14 12:26:14</t>
         </is>
       </c>
       <c r="D54" t="b">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1.018644750331112</v>
+        <v>0.9198294229759364</v>
       </c>
       <c r="F54" t="n">
-        <v>1.062929432154227</v>
+        <v>0.9683947417870724</v>
       </c>
     </row>
     <row r="55">
@@ -46825,17 +46825,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-07-02 11:47:12</t>
+          <t>2026-10-14 12:26:27</t>
         </is>
       </c>
       <c r="D55" t="b">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.018644750331112</v>
+        <v>0.9198294229759364</v>
       </c>
       <c r="F55" t="n">
-        <v>1.062929432154227</v>
+        <v>0.9683947417870724</v>
       </c>
     </row>
     <row r="56">
@@ -46851,17 +46851,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-07-02 11:47:24</t>
+          <t>2026-10-14 12:26:39</t>
         </is>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9236627243038589</v>
+        <v>0.8499577662383697</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9488238097350672</v>
+        <v>0.8628582477167764</v>
       </c>
     </row>
     <row r="57">
@@ -46877,17 +46877,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-07-02 11:47:36</t>
+          <t>2026-10-14 12:26:51</t>
         </is>
       </c>
       <c r="D57" t="b">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9236627243038589</v>
+        <v>0.8499577662383697</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9488238097350672</v>
+        <v>0.8628582477167764</v>
       </c>
     </row>
     <row r="58">
@@ -46903,17 +46903,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-07-02 11:47:54</t>
+          <t>2026-10-14 12:27:04</t>
         </is>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9302694361754914</v>
+        <v>0.834662135791385</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9597379902659438</v>
+        <v>0.8676677652272388</v>
       </c>
     </row>
     <row r="59">
@@ -46929,17 +46929,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-07-02 11:48:12</t>
+          <t>2026-10-14 12:27:16</t>
         </is>
       </c>
       <c r="D59" t="b">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9302694361754914</v>
+        <v>0.834662135791385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9597379902659438</v>
+        <v>0.8676677652272388</v>
       </c>
     </row>
     <row r="60">
@@ -46955,17 +46955,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-07-02 11:48:24</t>
+          <t>2026-10-14 12:27:29</t>
         </is>
       </c>
       <c r="D60" t="b">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9236627243038589</v>
+        <v>0.8499577662383697</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9488238097350672</v>
+        <v>0.8628582477167764</v>
       </c>
     </row>
     <row r="61">
@@ -46981,17 +46981,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-07-02 11:48:35</t>
+          <t>2026-10-14 12:27:42</t>
         </is>
       </c>
       <c r="D61" t="b">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9236627243038589</v>
+        <v>0.8499577662383697</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9488238097350672</v>
+        <v>0.8628582477167764</v>
       </c>
     </row>
     <row r="62">
@@ -47007,17 +47007,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-07-02 11:48:55</t>
+          <t>2026-10-14 12:27:54</t>
         </is>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9302694361754914</v>
+        <v>0.834662135791385</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9597379902659438</v>
+        <v>0.8676677652272388</v>
       </c>
     </row>
     <row r="63">
@@ -47033,17 +47033,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-07-02 11:49:13</t>
+          <t>2026-10-14 12:28:05</t>
         </is>
       </c>
       <c r="D63" t="b">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9302694361754914</v>
+        <v>0.834662135791385</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9597379902659438</v>
+        <v>0.8676677652272388</v>
       </c>
     </row>
     <row r="64">
@@ -47059,17 +47059,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-07-02 11:49:26</t>
+          <t>2026-10-14 12:28:25</t>
         </is>
       </c>
       <c r="D64" t="b">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.913978787474053</v>
+        <v>0.8411664030204196</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9361509814172533</v>
+        <v>0.8717115816532157</v>
       </c>
     </row>
     <row r="65">
@@ -47085,17 +47085,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-07-02 11:49:38</t>
+          <t>2026-10-14 12:28:44</t>
         </is>
       </c>
       <c r="D65" t="b">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.913978787474053</v>
+        <v>0.8411664030204196</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9361509814172533</v>
+        <v>0.8717115816532157</v>
       </c>
     </row>
     <row r="66">
@@ -47111,17 +47111,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-07-02 11:49:58</t>
+          <t>2026-10-14 12:28:56</t>
         </is>
       </c>
       <c r="D66" t="b">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9205092158741435</v>
+        <v>0.8253578730356395</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9469200082647193</v>
+        <v>0.8615256962809096</v>
       </c>
     </row>
     <row r="67">
@@ -47137,17 +47137,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-07-02 11:50:19</t>
+          <t>2026-10-14 12:29:09</t>
         </is>
       </c>
       <c r="D67" t="b">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9205092158741435</v>
+        <v>0.8253578730356395</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9469200082647193</v>
+        <v>0.8615256962809096</v>
       </c>
     </row>
     <row r="68">
@@ -47163,17 +47163,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-07-02 11:50:31</t>
+          <t>2026-10-14 12:29:27</t>
         </is>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.057833717085189</v>
+        <v>0.9786717642033345</v>
       </c>
       <c r="F68" t="n">
-        <v>1.094886639770707</v>
+        <v>1.005274003484212</v>
       </c>
     </row>
     <row r="69">
@@ -47189,17 +47189,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-07-02 11:50:44</t>
+          <t>2026-10-14 12:29:46</t>
         </is>
       </c>
       <c r="D69" t="b">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.057833717085189</v>
+        <v>0.9786717642033345</v>
       </c>
       <c r="F69" t="n">
-        <v>1.094886639770707</v>
+        <v>1.005274003484212</v>
       </c>
     </row>
     <row r="70">
@@ -47215,17 +47215,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-07-02 11:50:55</t>
+          <t>2026-10-14 12:30:02</t>
         </is>
       </c>
       <c r="D70" t="b">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1.068528912584134</v>
+        <v>0.9667623499454715</v>
       </c>
       <c r="F70" t="n">
-        <v>1.110844188258104</v>
+        <v>1.016729679730873</v>
       </c>
     </row>
     <row r="71">
@@ -47241,17 +47241,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-07-02 11:51:07</t>
+          <t>2026-10-14 12:30:15</t>
         </is>
       </c>
       <c r="D71" t="b">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.068528912584134</v>
+        <v>0.9667623499454715</v>
       </c>
       <c r="F71" t="n">
-        <v>1.110844188258104</v>
+        <v>1.016729679730873</v>
       </c>
     </row>
     <row r="72">
@@ -47267,17 +47267,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-07-02 11:51:19</t>
+          <t>2026-10-14 12:30:28</t>
         </is>
       </c>
       <c r="D72" t="b">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1.063235670489106</v>
+        <v>0.9836124347350654</v>
       </c>
       <c r="F72" t="n">
-        <v>1.101671618774417</v>
+        <v>1.014316586193813</v>
       </c>
     </row>
     <row r="73">
@@ -47293,17 +47293,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-07-02 11:51:33</t>
+          <t>2026-10-14 12:30:42</t>
         </is>
       </c>
       <c r="D73" t="b">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.063235670489106</v>
+        <v>0.9836124347350654</v>
       </c>
       <c r="F73" t="n">
-        <v>1.101671618774417</v>
+        <v>1.014316586193813</v>
       </c>
     </row>
     <row r="74">
@@ -47319,17 +47319,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-07-02 11:51:46</t>
+          <t>2026-10-14 12:30:54</t>
         </is>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.073992701934968</v>
+        <v>0.971633129156518</v>
       </c>
       <c r="F74" t="n">
-        <v>1.117824580660754</v>
+        <v>1.023019133223793</v>
       </c>
     </row>
     <row r="75">
@@ -47345,17 +47345,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-07-02 11:52:00</t>
+          <t>2026-10-14 12:31:06</t>
         </is>
       </c>
       <c r="D75" t="b">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1.073992701934968</v>
+        <v>0.971633129156518</v>
       </c>
       <c r="F75" t="n">
-        <v>1.117824580660754</v>
+        <v>1.023019133223793</v>
       </c>
     </row>
     <row r="76">
@@ -47371,17 +47371,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-07-02 11:52:15</t>
+          <t>2026-10-14 12:31:18</t>
         </is>
       </c>
       <c r="D76" t="b">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1.050214021054337</v>
+        <v>0.9716546351672947</v>
       </c>
       <c r="F76" t="n">
-        <v>1.090843428429197</v>
+        <v>1.014878723511173</v>
       </c>
     </row>
     <row r="77">
@@ -47397,17 +47397,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-07-02 11:52:28</t>
+          <t>2026-10-14 12:31:30</t>
         </is>
       </c>
       <c r="D77" t="b">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.050214021054337</v>
+        <v>0.9716546351672947</v>
       </c>
       <c r="F77" t="n">
-        <v>1.090843428429197</v>
+        <v>1.014878723511173</v>
       </c>
     </row>
     <row r="78">
@@ -47423,17 +47423,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-07-02 11:52:40</t>
+          <t>2026-10-14 12:31:43</t>
         </is>
       </c>
       <c r="D78" t="b">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>1.060442762864342</v>
+        <v>0.9575532354219365</v>
       </c>
       <c r="F78" t="n">
-        <v>1.106484240840502</v>
+        <v>1.007931180218232</v>
       </c>
     </row>
     <row r="79">
@@ -47449,17 +47449,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-07-02 11:52:53</t>
+          <t>2026-10-14 12:31:54</t>
         </is>
       </c>
       <c r="D79" t="b">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>1.060442762864342</v>
+        <v>0.9575532354219365</v>
       </c>
       <c r="F79" t="n">
-        <v>1.106484240840502</v>
+        <v>1.007931180218232</v>
       </c>
     </row>
     <row r="80">
@@ -47475,17 +47475,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-07-02 11:53:07</t>
+          <t>2026-10-14 12:32:07</t>
         </is>
       </c>
       <c r="D80" t="b">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9580301509366255</v>
+        <v>0.8816493080255507</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9833871886203733</v>
+        <v>0.9104756041194316</v>
       </c>
     </row>
     <row r="81">
@@ -47501,17 +47501,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-07-02 11:53:20</t>
+          <t>2026-10-14 12:32:19</t>
         </is>
       </c>
       <c r="D81" t="b">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9580301509366255</v>
+        <v>0.8816493080255507</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9833871886203733</v>
+        <v>0.9104756041194316</v>
       </c>
     </row>
     <row r="82">
@@ -47527,17 +47527,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-07-02 11:53:46</t>
+          <t>2026-10-14 12:32:30</t>
         </is>
       </c>
       <c r="D82" t="b">
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9648811251811126</v>
+        <v>0.8657909150343661</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9947495029421329</v>
+        <v>0.9053011216186642</v>
       </c>
     </row>
     <row r="83">
@@ -47553,17 +47553,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-07-02 11:54:06</t>
+          <t>2026-10-14 12:32:42</t>
         </is>
       </c>
       <c r="D83" t="b">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9648811251811126</v>
+        <v>0.8657909150343661</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9947495029421329</v>
+        <v>0.9053011216186642</v>
       </c>
     </row>
     <row r="84">
@@ -47579,17 +47579,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-07-02 11:54:18</t>
+          <t>2026-10-14 12:32:53</t>
         </is>
       </c>
       <c r="D84" t="b">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9628496121631855</v>
+        <v>0.8860042491625372</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9899181302031312</v>
+        <v>0.8993751096219458</v>
       </c>
     </row>
     <row r="85">
@@ -47605,17 +47605,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-07-02 11:54:31</t>
+          <t>2026-10-14 12:33:04</t>
         </is>
       </c>
       <c r="D85" t="b">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9628496121631855</v>
+        <v>0.8860042491625372</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9899181302031312</v>
+        <v>0.8993751096219458</v>
       </c>
     </row>
     <row r="86">
@@ -47631,17 +47631,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-07-02 11:54:43</t>
+          <t>2026-10-14 12:33:15</t>
         </is>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9697408537539894</v>
+        <v>0.8700489455919085</v>
       </c>
       <c r="F86" t="n">
-        <v>1.001190978048176</v>
+        <v>0.9049907605876555</v>
       </c>
     </row>
     <row r="87">
@@ -47657,17 +47657,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-07-02 11:54:53</t>
+          <t>2026-10-14 12:33:27</t>
         </is>
       </c>
       <c r="D87" t="b">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9697408537539894</v>
+        <v>0.8700489455919085</v>
       </c>
       <c r="F87" t="n">
-        <v>1.001190978048176</v>
+        <v>0.9049907605876555</v>
       </c>
     </row>
     <row r="88">
@@ -47683,17 +47683,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-07-02 11:55:05</t>
+          <t>2026-10-14 12:33:43</t>
         </is>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9511720014082856</v>
+        <v>0.875402228430365</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9744709870175174</v>
+        <v>0.907481487513068</v>
       </c>
     </row>
     <row r="89">
@@ -47709,17 +47709,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-07-02 11:55:16</t>
+          <t>2026-10-14 12:34:00</t>
         </is>
       </c>
       <c r="D89" t="b">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9511720014082856</v>
+        <v>0.875402228430365</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9744709870175174</v>
+        <v>0.907481487513068</v>
       </c>
     </row>
     <row r="90">
@@ -47735,17 +47735,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-07-02 11:55:34</t>
+          <t>2026-10-14 12:34:12</t>
         </is>
       </c>
       <c r="D90" t="b">
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9579701296384895</v>
+        <v>0.8592176880911819</v>
       </c>
       <c r="F90" t="n">
-        <v>0.985684904138356</v>
+        <v>0.896910679959495</v>
       </c>
     </row>
     <row r="91">
@@ -47761,17 +47761,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-07-02 11:55:51</t>
+          <t>2026-10-14 12:34:24</t>
         </is>
       </c>
       <c r="D91" t="b">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9579701296384895</v>
+        <v>0.8592176880911819</v>
       </c>
       <c r="F91" t="n">
-        <v>0.985684904138356</v>
+        <v>0.896910679959495</v>
       </c>
     </row>
     <row r="92">
@@ -47787,17 +47787,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-07-02 11:56:07</t>
+          <t>2026-10-14 12:34:35</t>
         </is>
       </c>
       <c r="D92" t="b">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0.8599459773969473</v>
+        <v>0.7888831311646057</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8738603076434093</v>
+        <v>0.8151759063209761</v>
       </c>
     </row>
     <row r="93">
@@ -47813,17 +47813,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-07-02 11:56:21</t>
+          <t>2026-10-14 12:34:46</t>
         </is>
       </c>
       <c r="D93" t="b">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0.8599459773969473</v>
+        <v>0.7888831311646057</v>
       </c>
       <c r="F93" t="n">
-        <v>0.8738603076434093</v>
+        <v>0.8151759063209761</v>
       </c>
     </row>
     <row r="94">
@@ -47839,17 +47839,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-07-02 11:56:36</t>
+          <t>2026-10-14 12:34:58</t>
         </is>
       </c>
       <c r="D94" t="b">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8599459773969473</v>
+        <v>0.7888831311646057</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8738603076434093</v>
+        <v>0.8151759063209761</v>
       </c>
     </row>
     <row r="95">
@@ -47865,17 +47865,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-07-02 11:56:50</t>
+          <t>2026-10-14 12:35:09</t>
         </is>
       </c>
       <c r="D95" t="b">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0.8599459773969473</v>
+        <v>0.7888831311646057</v>
       </c>
       <c r="F95" t="n">
-        <v>0.8738603076434093</v>
+        <v>0.8151759063209761</v>
       </c>
     </row>
     <row r="96">
@@ -47891,17 +47891,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-07-02 11:57:06</t>
+          <t>2026-10-14 12:35:20</t>
         </is>
       </c>
       <c r="D96" t="b">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0.8510344917483862</v>
+        <v>0.7808316785485443</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8623716890765403</v>
+        <v>0.8050507489350874</v>
       </c>
     </row>
     <row r="97">
@@ -47917,17 +47917,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-07-02 11:57:20</t>
+          <t>2026-10-14 12:35:32</t>
         </is>
       </c>
       <c r="D97" t="b">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8510344917483862</v>
+        <v>0.7808316785485443</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8623716890765403</v>
+        <v>0.8050507489350874</v>
       </c>
     </row>
     <row r="98">
@@ -47943,17 +47943,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-07-02 11:57:40</t>
+          <t>2026-10-14 12:35:45</t>
         </is>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>0.7921227979897406</v>
+        <v>0.7230621354358511</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8573206800438894</v>
+        <v>0.737668982986143</v>
       </c>
     </row>
     <row r="99">
@@ -47969,17 +47969,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-07-02 11:57:58</t>
+          <t>2026-10-14 12:35:59</t>
         </is>
       </c>
       <c r="D99" t="b">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7921227979897406</v>
+        <v>0.7230621354358511</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8573206800438894</v>
+        <v>0.737668982986143</v>
       </c>
     </row>
     <row r="100">
@@ -47995,17 +47995,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-07-02 11:58:17</t>
+          <t>2026-10-14 12:36:13</t>
         </is>
       </c>
       <c r="D100" t="b">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7921227979897406</v>
+        <v>0.7230621354358511</v>
       </c>
       <c r="F100" t="n">
-        <v>0.8573206800438894</v>
+        <v>0.737668982986143</v>
       </c>
     </row>
     <row r="101">
@@ -48021,17 +48021,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-07-02 11:58:34</t>
+          <t>2026-10-14 12:36:31</t>
         </is>
       </c>
       <c r="D101" t="b">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7921227979897406</v>
+        <v>0.7230621354358511</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8573206800438894</v>
+        <v>0.737668982986143</v>
       </c>
     </row>
     <row r="102">
@@ -48047,17 +48047,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-07-02 11:58:45</t>
+          <t>2026-10-14 12:36:48</t>
         </is>
       </c>
       <c r="D102" t="b">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0.78403188153182</v>
+        <v>0.7158167830299699</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8447398459906701</v>
+        <v>0.7841055196796785</v>
       </c>
     </row>
     <row r="103">
@@ -48073,17 +48073,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-07-02 11:58:56</t>
+          <t>2026-10-14 12:37:04</t>
         </is>
       </c>
       <c r="D103" t="b">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>0.78403188153182</v>
+        <v>0.7158167830299699</v>
       </c>
       <c r="F103" t="n">
-        <v>0.8447398459906701</v>
+        <v>0.7841055196796785</v>
       </c>
     </row>
   </sheetData>
